--- a/META.xlsx
+++ b/META.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECA3BDB-91BB-4B5D-8EFC-43109FE1DE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37181A1F-B826-4372-8BEA-A86C2B15B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22310" yWindow="6660" windowWidth="15770" windowHeight="13220" xr2:uid="{DF105585-55F7-489F-BFB3-1F48B85ABA8A}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="24170" windowHeight="12950" activeTab="1" xr2:uid="{DF105585-55F7-489F-BFB3-1F48B85ABA8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1559,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="17">
-        <v>605</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="M4" s="3">
         <f>+M3*M2</f>
-        <v>1551220</v>
+        <v>1507632</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="M7" s="3">
         <f>+M4-M5+M6</f>
-        <v>1500378</v>
+        <v>1456790</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -3761,6 +3761,24 @@
       <c r="BN19" s="3">
         <v>20982</v>
       </c>
+      <c r="BO19" s="3">
+        <v>18259</v>
+      </c>
+      <c r="BP19" s="3">
+        <v>20045</v>
+      </c>
+      <c r="BQ19" s="3">
+        <v>21331</v>
+      </c>
+      <c r="BR19" s="3">
+        <v>25643</v>
+      </c>
+      <c r="BS19" s="3">
+        <v>23667</v>
+      </c>
+      <c r="BT19" s="3">
+        <v>26337</v>
+      </c>
     </row>
     <row r="20" spans="2:103" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
@@ -3854,6 +3872,24 @@
       <c r="BN20" s="3">
         <v>11154</v>
       </c>
+      <c r="BO20" s="3">
+        <v>9527</v>
+      </c>
+      <c r="BP20" s="3">
+        <v>11366</v>
+      </c>
+      <c r="BQ20" s="3">
+        <v>12072</v>
+      </c>
+      <c r="BR20" s="3">
+        <v>14198</v>
+      </c>
+      <c r="BS20" s="3">
+        <v>13296</v>
+      </c>
+      <c r="BT20" s="3">
+        <v>14085</v>
+      </c>
     </row>
     <row r="21" spans="2:103" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
@@ -3947,6 +3983,24 @@
       <c r="BN21" s="3">
         <v>9012</v>
       </c>
+      <c r="BO21" s="3">
+        <v>8224</v>
+      </c>
+      <c r="BP21" s="3">
+        <v>9148</v>
+      </c>
+      <c r="BQ21" s="3">
+        <v>10020</v>
+      </c>
+      <c r="BR21" s="3">
+        <v>10893</v>
+      </c>
+      <c r="BS21" s="3">
+        <v>10631</v>
+      </c>
+      <c r="BT21" s="3">
+        <v>10847</v>
+      </c>
     </row>
     <row r="22" spans="2:103" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
@@ -4039,6 +4093,24 @@
       </c>
       <c r="BN22" s="3">
         <v>5635</v>
+      </c>
+      <c r="BO22" s="3">
+        <v>5382</v>
+      </c>
+      <c r="BP22" s="3">
+        <v>6004</v>
+      </c>
+      <c r="BQ22" s="3">
+        <v>6659</v>
+      </c>
+      <c r="BR22" s="3">
+        <v>7403</v>
+      </c>
+      <c r="BS22" s="3">
+        <v>7430</v>
+      </c>
+      <c r="BT22" s="3">
+        <v>8094</v>
       </c>
     </row>
     <row r="23" spans="2:103" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4629,6 +4701,18 @@
       <c r="BP29" s="3">
         <v>583</v>
       </c>
+      <c r="BQ29" s="3">
+        <v>690</v>
+      </c>
+      <c r="BR29" s="3">
+        <v>801</v>
+      </c>
+      <c r="BS29" s="3">
+        <v>885</v>
+      </c>
+      <c r="BT29" s="3">
+        <v>1007</v>
+      </c>
       <c r="CM29" s="3">
         <v>825</v>
       </c>
@@ -4762,6 +4846,18 @@
       <c r="BP30" s="3">
         <v>370</v>
       </c>
+      <c r="BQ30" s="3">
+        <v>470</v>
+      </c>
+      <c r="BR30" s="3">
+        <v>955</v>
+      </c>
+      <c r="BS30" s="3">
+        <v>402</v>
+      </c>
+      <c r="BT30" s="3">
+        <v>431</v>
+      </c>
       <c r="CN30" s="3">
         <v>501</v>
       </c>
@@ -4928,42 +5024,65 @@
         <v>27237</v>
       </c>
       <c r="BF31" s="6">
+        <f>SUM(BF19:BF22)</f>
         <v>31254</v>
       </c>
       <c r="BG31" s="6">
+        <f>SUM(BG19:BG22)</f>
         <v>28101</v>
       </c>
       <c r="BH31" s="6">
+        <f>SUM(BH19:BH22)</f>
         <v>31498</v>
       </c>
       <c r="BI31" s="6">
+        <f>SUM(BI19:BI22)</f>
         <v>33643</v>
       </c>
       <c r="BJ31" s="6">
+        <f>SUM(BJ19:BJ22)</f>
         <v>38706</v>
       </c>
       <c r="BK31" s="6">
+        <f>SUM(BK19:BK22)</f>
         <v>35635</v>
       </c>
       <c r="BL31" s="6">
+        <f>SUM(BL19:BL22)</f>
         <v>38329</v>
       </c>
       <c r="BM31" s="6">
+        <f>SUM(BM19:BM22)</f>
         <v>39885</v>
       </c>
       <c r="BN31" s="6">
+        <f>SUM(BN19:BN22)</f>
         <v>46783</v>
       </c>
       <c r="BO31" s="6">
+        <f>SUM(BO19:BO22)</f>
         <v>41392</v>
       </c>
       <c r="BP31" s="6">
+        <f>SUM(BP19:BP22)</f>
         <v>46563</v>
       </c>
-      <c r="BQ31" s="6"/>
-      <c r="BR31" s="6"/>
-      <c r="BS31" s="6"/>
-      <c r="BT31" s="6"/>
+      <c r="BQ31" s="6">
+        <f>SUM(BQ19:BQ22)</f>
+        <v>50082</v>
+      </c>
+      <c r="BR31" s="6">
+        <f>SUM(BR19:BR22)</f>
+        <v>58137</v>
+      </c>
+      <c r="BS31" s="6">
+        <f>SUM(BS19:BS22)</f>
+        <v>55024</v>
+      </c>
+      <c r="BT31" s="6">
+        <f>SUM(BT19:BT22)</f>
+        <v>59363</v>
+      </c>
       <c r="BU31" s="6"/>
       <c r="BV31" s="6"/>
       <c r="BW31" s="6"/>
@@ -5305,9 +5424,15 @@
       <c r="BS32" s="8">
         <v>56311</v>
       </c>
-      <c r="BT32" s="8"/>
-      <c r="BU32" s="8"/>
-      <c r="BV32" s="8"/>
+      <c r="BT32" s="8">
+        <v>60801</v>
+      </c>
+      <c r="BU32" s="8">
+        <v>63140</v>
+      </c>
+      <c r="BV32" s="8">
+        <v>73330</v>
+      </c>
       <c r="BW32" s="8"/>
       <c r="BY32" s="7">
         <f t="shared" ref="BY32:CA32" si="23">SUM(BY29:BY31)</f>
@@ -9197,64 +9322,73 @@
         <f t="shared" si="178"/>
         <v>0.33078886420570019</v>
       </c>
-      <c r="BT47" s="11"/>
-      <c r="BU47" s="11"/>
-      <c r="BV47" s="11"/>
+      <c r="BT47" s="11">
+        <f t="shared" ref="BT47" si="179">+BT32/BP32-1</f>
+        <v>0.27959003283104633</v>
+      </c>
+      <c r="BU47" s="11">
+        <f t="shared" ref="BU47" si="180">+BU32/BQ32-1</f>
+        <v>0.23219234221927332</v>
+      </c>
+      <c r="BV47" s="11">
+        <f t="shared" ref="BV47" si="181">+BV32/BR32-1</f>
+        <v>0.22435009099560888</v>
+      </c>
       <c r="BW47" s="11"/>
       <c r="BZ47" s="18">
-        <f t="shared" ref="BZ47:CL47" si="179">+BZ32/BY32-1</f>
+        <f t="shared" ref="BZ47:CL47" si="182">+BZ32/BY32-1</f>
         <v>22.560209424083769</v>
       </c>
       <c r="CA47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>4.333333333333333</v>
       </c>
       <c r="CB47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>2.1875</v>
       </c>
       <c r="CC47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.77777777777777768</v>
       </c>
       <c r="CD47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>1.8566176470588234</v>
       </c>
       <c r="CE47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>1.5405405405405403</v>
       </c>
       <c r="CF47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.87993920972644379</v>
       </c>
       <c r="CG47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.37132848288870934</v>
       </c>
       <c r="CH47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.5468657889565729</v>
       </c>
       <c r="CI47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.58358739837398366</v>
       </c>
       <c r="CJ47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.43815177282207607</v>
       </c>
       <c r="CK47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.54161088799643009</v>
       </c>
       <c r="CL47" s="18">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0.47090961719371882</v>
       </c>
       <c r="CM47" s="18">
-        <f t="shared" ref="CM47" si="180">+CM32/CL32-1</f>
+        <f t="shared" ref="CM47" si="183">+CM32/CL32-1</f>
         <v>0.37352716896661997</v>
       </c>
       <c r="CN47" s="18">
@@ -9274,35 +9408,35 @@
         <v>-1.1193175554782941E-2</v>
       </c>
       <c r="CR47" s="18">
-        <f t="shared" ref="CR47:CY47" si="181">+CR32/CQ32-1</f>
+        <f t="shared" ref="CR47:CY47" si="184">+CR32/CQ32-1</f>
         <v>0.15686610810486323</v>
       </c>
       <c r="CS47" s="18">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>0.21941275453851339</v>
       </c>
       <c r="CT47" s="18">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>0.22167173252279637</v>
       </c>
       <c r="CU47" s="18">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="CV47" s="18">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="CW47" s="18">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="CX47" s="18">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CY47" s="18">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -9363,15 +9497,15 @@
         <v>0.41985917173887088</v>
       </c>
       <c r="AZ48" s="11">
-        <f t="shared" ref="AZ48:BB48" si="182">+AZ27/AV27-1</f>
+        <f t="shared" ref="AZ48:BB48" si="185">+AZ27/AV27-1</f>
         <v>0.47543879015343848</v>
       </c>
       <c r="BA48" s="11">
-        <f t="shared" si="182"/>
+        <f t="shared" si="185"/>
         <v>0.31097316780136164</v>
       </c>
       <c r="BB48" s="11">
-        <f t="shared" si="182"/>
+        <f t="shared" si="185"/>
         <v>0.14539923954372624</v>
       </c>
       <c r="BC48" s="11">
@@ -9383,7 +9517,7 @@
         <v>-1</v>
       </c>
       <c r="BE48" s="11">
-        <f t="shared" ref="BE48" si="183">+BE27/BA27-1</f>
+        <f t="shared" ref="BE48" si="186">+BE27/BA27-1</f>
         <v>-1</v>
       </c>
       <c r="BF48" s="11"/>
@@ -9589,72 +9723,72 @@
       <c r="AZ51" s="10"/>
       <c r="BA51" s="10"/>
       <c r="BB51" s="10">
-        <f t="shared" ref="BB51" si="184">+BB30/AX30-1</f>
+        <f t="shared" ref="BB51" si="187">+BB30/AX30-1</f>
         <v>0.22315202231520215</v>
       </c>
       <c r="BC51" s="10">
-        <f t="shared" ref="BC51:BK51" si="185">+BC30/AY30-1</f>
+        <f t="shared" ref="BC51:BK51" si="188">+BC30/AY30-1</f>
         <v>0.30149812734082393</v>
       </c>
       <c r="BD51" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>0.4819672131147541</v>
       </c>
       <c r="BE51" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>-0.489247311827957</v>
       </c>
       <c r="BF51" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>-0.17103762827822122</v>
       </c>
       <c r="BG51" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>-0.51223021582733819</v>
       </c>
       <c r="BH51" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>-0.38938053097345138</v>
       </c>
       <c r="BI51" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>-0.26315789473684215</v>
       </c>
       <c r="BJ51" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>0.47317744154057761</v>
       </c>
       <c r="BK51" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>0.29793510324483785</v>
       </c>
       <c r="BL51" s="10">
-        <f t="shared" ref="BL51" si="186">+BL30/BH30-1</f>
+        <f t="shared" ref="BL51" si="189">+BL30/BH30-1</f>
         <v>0.27898550724637672</v>
       </c>
       <c r="BM51" s="10">
-        <f t="shared" ref="BM51" si="187">+BM30/BI30-1</f>
+        <f t="shared" ref="BM51" si="190">+BM30/BI30-1</f>
         <v>0.28571428571428581</v>
       </c>
       <c r="BN51" s="10">
-        <f t="shared" ref="BN51" si="188">+BN30/BJ30-1</f>
+        <f t="shared" ref="BN51" si="191">+BN30/BJ30-1</f>
         <v>1.1204481792717047E-2</v>
       </c>
       <c r="BO51" s="10">
-        <f t="shared" ref="BO51" si="189">+BO30/BK30-1</f>
+        <f t="shared" ref="BO51" si="192">+BO30/BK30-1</f>
         <v>-6.3636363636363602E-2</v>
       </c>
       <c r="BP51" s="10">
-        <f t="shared" ref="BP51" si="190">+BP30/BL30-1</f>
+        <f t="shared" ref="BP51" si="193">+BP30/BL30-1</f>
         <v>4.8158640226628968E-2</v>
       </c>
       <c r="BQ51" s="10">
-        <f t="shared" ref="BQ51" si="191">+BQ30/BM30-1</f>
-        <v>-1</v>
+        <f t="shared" ref="BQ51" si="194">+BQ30/BM30-1</f>
+        <v>0.7407407407407407</v>
       </c>
       <c r="BR51" s="10">
-        <f t="shared" ref="BR51" si="192">+BR30/BN30-1</f>
-        <v>-1</v>
+        <f t="shared" ref="BR51" si="195">+BR30/BN30-1</f>
+        <v>-0.11819021237303784</v>
       </c>
       <c r="BS51" s="10"/>
       <c r="BT51" s="10"/>
@@ -9662,7 +9796,7 @@
       <c r="BV51" s="10"/>
       <c r="BW51" s="10"/>
       <c r="CO51" s="19">
-        <f t="shared" ref="CO51" si="193">CO30/CN30-1</f>
+        <f t="shared" ref="CO51" si="196">CO30/CN30-1</f>
         <v>1.2734530938123751</v>
       </c>
       <c r="CP51" s="19">
@@ -9729,19 +9863,19 @@
       <c r="AY52" s="6"/>
       <c r="AZ52" s="6"/>
       <c r="BA52" s="10">
-        <f t="shared" ref="BA52:BD52" si="194">+BA38/AW38-1</f>
+        <f t="shared" ref="BA52:BD52" si="197">+BA38/AW38-1</f>
         <v>0.38761368557817244</v>
       </c>
       <c r="BB52" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="197"/>
         <v>0.46108852979081982</v>
       </c>
       <c r="BC52" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="197"/>
         <v>0.38470296004967919</v>
       </c>
       <c r="BD52" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="197"/>
         <v>0.35019008045265676</v>
       </c>
       <c r="BE52" s="10">
@@ -9749,23 +9883,23 @@
         <v>0.27450062421972543</v>
       </c>
       <c r="BF52" s="10">
-        <f t="shared" ref="BF52:BJ52" si="195">+BF38/BB38-1</f>
+        <f t="shared" ref="BF52:BJ52" si="198">+BF38/BB38-1</f>
         <v>0.18265707694395439</v>
       </c>
       <c r="BG52" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="198"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="BH52" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="198"/>
         <v>-3.1430068098480923E-2</v>
       </c>
       <c r="BI52" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="198"/>
         <v>-0.13138239255540585</v>
       </c>
       <c r="BJ52" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="198"/>
         <v>-8.0206540447504304E-2</v>
       </c>
       <c r="BK52" s="10">
@@ -9773,31 +9907,31 @@
         <v>0.32853310744035014</v>
       </c>
       <c r="BL52" s="10">
-        <f t="shared" ref="BL52:BO52" si="196">+BL38/BH38-1</f>
+        <f t="shared" ref="BL52:BO52" si="199">+BL38/BH38-1</f>
         <v>0.14359113034072468</v>
       </c>
       <c r="BM52" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="199"/>
         <v>0.11812799548914565</v>
       </c>
       <c r="BN52" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="199"/>
         <v>9.2939121756487886E-3</v>
       </c>
       <c r="BO52" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="199"/>
         <v>7.4388947927736426E-2</v>
       </c>
       <c r="BP52" s="10">
-        <f t="shared" ref="BP52" si="197">+BP38/BL38-1</f>
+        <f t="shared" ref="BP52" si="200">+BP38/BL38-1</f>
         <v>9.8604871127926152E-2</v>
       </c>
       <c r="BQ52" s="10">
-        <f t="shared" ref="BQ52" si="198">+BQ38/BM38-1</f>
+        <f t="shared" ref="BQ52" si="201">+BQ38/BM38-1</f>
         <v>0.35533282904689867</v>
       </c>
       <c r="BR52" s="10">
-        <f t="shared" ref="BR52" si="199">+BR38/BN38-1</f>
+        <f t="shared" ref="BR52" si="202">+BR38/BN38-1</f>
         <v>0.49823867498918495</v>
       </c>
       <c r="BS52" s="10"/>
@@ -9922,99 +10056,99 @@
       <c r="AK54" s="10"/>
       <c r="AL54" s="10"/>
       <c r="AM54" s="10">
-        <f t="shared" ref="AM54:BJ54" si="200">+AM34/AM32</f>
+        <f t="shared" ref="AM54:BJ54" si="203">+AM34/AM32</f>
         <v>0.8389603877653351</v>
       </c>
       <c r="AN54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.83266570931902351</v>
       </c>
       <c r="AO54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.82385080498288044</v>
       </c>
       <c r="AP54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.83469315360056762</v>
       </c>
       <c r="AQ54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.81322544272733299</v>
       </c>
       <c r="AR54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.80415729006277392</v>
       </c>
       <c r="AS54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.82126671198731027</v>
       </c>
       <c r="AT54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.83436106631249407</v>
       </c>
       <c r="AU54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.80498393189378137</v>
       </c>
       <c r="AV54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.7950981966072671</v>
       </c>
       <c r="AW54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.80465766185374943</v>
       </c>
       <c r="AX54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.81440581362211462</v>
       </c>
       <c r="AY54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.80394329601467274</v>
       </c>
       <c r="AZ54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.81432059703545756</v>
       </c>
       <c r="BA54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.80106859703550504</v>
       </c>
       <c r="BB54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.81146981081642955</v>
       </c>
       <c r="BC54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.78482872294682526</v>
       </c>
       <c r="BD54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.81985982929706469</v>
       </c>
       <c r="BE54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.79375045103557773</v>
       </c>
       <c r="BF54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.74083631276231932</v>
       </c>
       <c r="BG54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.78999999999999992</v>
       </c>
       <c r="BH54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="BI54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.81813389562467054</v>
       </c>
       <c r="BJ54" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>0.79</v>
       </c>
       <c r="BK54" s="10">
@@ -10022,35 +10156,35 @@
         <v>0.81785763269784661</v>
       </c>
       <c r="BL54" s="10">
-        <f t="shared" ref="BL54:BO54" si="201">+BL34/BL32</f>
+        <f t="shared" ref="BL54:BO54" si="204">+BL34/BL32</f>
         <v>0.81295590079598679</v>
       </c>
       <c r="BM54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="204"/>
         <v>0.81830052477272164</v>
       </c>
       <c r="BN54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="204"/>
         <v>0.81731941717474421</v>
       </c>
       <c r="BO54" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="204"/>
         <v>0.82105213404546962</v>
       </c>
       <c r="BP54" s="10">
-        <f t="shared" ref="BP54:BR54" si="202">+BP34/BP32</f>
+        <f t="shared" ref="BP54:BR54" si="205">+BP34/BP32</f>
         <v>0.82130229817324696</v>
       </c>
       <c r="BQ54" s="10">
-        <f t="shared" si="202"/>
+        <f t="shared" si="205"/>
         <v>0.82034268763904605</v>
       </c>
       <c r="BR54" s="10">
-        <f t="shared" si="202"/>
+        <f t="shared" si="205"/>
         <v>0.8179253001185447</v>
       </c>
       <c r="BS54" s="10">
-        <f t="shared" ref="BS54" si="203">+BS34/BS32</f>
+        <f t="shared" ref="BS54" si="206">+BS34/BS32</f>
         <v>0.83</v>
       </c>
       <c r="BT54" s="10"/>
@@ -10058,55 +10192,55 @@
       <c r="BV54" s="10"/>
       <c r="BW54" s="10"/>
       <c r="CM54" s="19">
-        <f t="shared" ref="CM54:CY54" si="204">+CM34/CM32</f>
+        <f t="shared" ref="CM54:CY54" si="207">+CM34/CM32</f>
         <v>0.8324617643898421</v>
       </c>
       <c r="CN54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81936998741106415</v>
       </c>
       <c r="CO54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.80582795323678236</v>
       </c>
       <c r="CP54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.80794376277251567</v>
       </c>
       <c r="CQ54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81</v>
       </c>
       <c r="CR54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81</v>
       </c>
       <c r="CS54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81</v>
       </c>
       <c r="CT54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81000000000000016</v>
       </c>
       <c r="CU54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81</v>
       </c>
       <c r="CV54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81</v>
       </c>
       <c r="CW54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81</v>
       </c>
       <c r="CX54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81</v>
       </c>
       <c r="CY54" s="19">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>0.81</v>
       </c>
     </row>
@@ -10151,75 +10285,75 @@
       <c r="AK55" s="10"/>
       <c r="AL55" s="10"/>
       <c r="AM55" s="10">
-        <f t="shared" ref="AM55:AO55" si="205">+AM39/AM32</f>
+        <f t="shared" ref="AM55:AO55" si="208">+AM39/AM32</f>
         <v>0.45537355841551064</v>
       </c>
       <c r="AN55" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="208"/>
         <v>0.44312599198851182</v>
       </c>
       <c r="AO55" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="208"/>
         <v>0.42114081736723247</v>
       </c>
       <c r="AP55" s="10">
-        <f t="shared" ref="AP55:AS55" si="206">+AP39/AP32</f>
+        <f t="shared" ref="AP55:AS55" si="209">+AP39/AP32</f>
         <v>0.46233889085964291</v>
       </c>
       <c r="AQ55" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="209"/>
         <v>0.41898255621144792</v>
       </c>
       <c r="AR55" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="209"/>
         <v>0.39239606774843067</v>
       </c>
       <c r="AS55" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="209"/>
         <v>0.40703602991162474</v>
       </c>
       <c r="AT55" s="10">
-        <f t="shared" ref="AT55:AV55" si="207">+AT39/AT32</f>
+        <f t="shared" ref="AT55:AV55" si="210">+AT39/AT32</f>
         <v>0.42016886443411439</v>
       </c>
       <c r="AU55" s="10">
-        <f t="shared" si="207"/>
+        <f t="shared" si="210"/>
         <v>0.33224333314540228</v>
       </c>
       <c r="AV55" s="10">
-        <f t="shared" si="207"/>
+        <f t="shared" si="210"/>
         <v>0.31909883876491679</v>
       </c>
       <c r="AW55" s="10">
-        <f t="shared" ref="AW55:AZ55" si="208">+AW39/AW32</f>
+        <f t="shared" ref="AW55:AZ55" si="211">+AW39/AW32</f>
         <v>0.37447601304145317</v>
       </c>
       <c r="AX55" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="211"/>
         <v>0.45507979481333716</v>
       </c>
       <c r="AY55" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="211"/>
         <v>0.43475602766420846</v>
       </c>
       <c r="AZ55" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="211"/>
         <v>0.42531898063761736</v>
       </c>
       <c r="BA55" s="10">
-        <f t="shared" ref="BA55:BD55" si="209">+BA39/BA32</f>
+        <f t="shared" ref="BA55:BD55" si="212">+BA39/BA32</f>
         <v>0.35928990003447087</v>
       </c>
       <c r="BB55" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="212"/>
         <v>0.37376377297971547</v>
       </c>
       <c r="BC55" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="212"/>
         <v>0.30543213415508097</v>
       </c>
       <c r="BD55" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="212"/>
         <v>0.28998681562695161</v>
       </c>
       <c r="BE55" s="10">
@@ -10227,23 +10361,23 @@
         <v>0.20437324096124701</v>
       </c>
       <c r="BF55" s="10">
-        <f t="shared" ref="BF55:BJ55" si="210">+BF39/BF32</f>
+        <f t="shared" ref="BF55:BJ55" si="213">+BF39/BF32</f>
         <v>0.19894295041193844</v>
       </c>
       <c r="BG55" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="213"/>
         <v>0.36964391691394655</v>
       </c>
       <c r="BH55" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="213"/>
         <v>0.35194849839057468</v>
       </c>
       <c r="BI55" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="213"/>
         <v>0.40262402624026239</v>
       </c>
       <c r="BJ55" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="213"/>
         <v>0.39030914213058771</v>
       </c>
       <c r="BK55" s="10">
@@ -10251,35 +10385,35 @@
         <v>0.37904265532848719</v>
       </c>
       <c r="BL55" s="10">
-        <f t="shared" ref="BL55:BO55" si="211">+BL39/BL32</f>
+        <f t="shared" ref="BL55:BO55" si="214">+BL39/BL32</f>
         <v>0.38000051188861306</v>
       </c>
       <c r="BM55" s="10">
-        <f t="shared" si="211"/>
+        <f t="shared" si="214"/>
         <v>0.4274557146024785</v>
       </c>
       <c r="BN55" s="10">
-        <f t="shared" si="211"/>
+        <f t="shared" si="214"/>
         <v>0.48289759222899659</v>
       </c>
       <c r="BO55" s="10">
-        <f t="shared" si="211"/>
+        <f t="shared" si="214"/>
         <v>0.41487450961856598</v>
       </c>
       <c r="BP55" s="10">
-        <f t="shared" ref="BP55:BR55" si="212">+BP39/BP32</f>
+        <f t="shared" ref="BP55:BR55" si="215">+BP39/BP32</f>
         <v>0.43019193534809325</v>
       </c>
       <c r="BQ55" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="215"/>
         <v>0.4007454822216151</v>
       </c>
       <c r="BR55" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="215"/>
         <v>0.41315345699831368</v>
       </c>
       <c r="BS55" s="10">
-        <f t="shared" ref="BS55" si="213">+BS39/BS32</f>
+        <f t="shared" ref="BS55" si="216">+BS39/BS32</f>
         <v>0.41762941521194791</v>
       </c>
       <c r="BT55" s="10"/>
@@ -10287,55 +10421,55 @@
       <c r="BV55" s="10"/>
       <c r="BW55" s="10"/>
       <c r="CM55" s="10">
-        <f t="shared" ref="CM55:CY55" si="214">+CM39/CM32</f>
+        <f t="shared" ref="CM55:CY55" si="217">+CM39/CM32</f>
         <v>0.44616569361366809</v>
       </c>
       <c r="CN55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.41000325332050863</v>
       </c>
       <c r="CO55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.3800500203571221</v>
       </c>
       <c r="CP55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.39645040660058173</v>
       </c>
       <c r="CQ55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.4149918959943058</v>
       </c>
       <c r="CR55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.48500203853196056</v>
       </c>
       <c r="CS55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.55562009118541034</v>
       </c>
       <c r="CT55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.61072079466573792</v>
       </c>
       <c r="CU55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.63615457259631369</v>
       </c>
       <c r="CV55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.65512991711038016</v>
       </c>
       <c r="CW55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.67168336297480946</v>
       </c>
       <c r="CX55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.68262551624776613</v>
       </c>
       <c r="CY55" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>0.69242437935325629</v>
       </c>
       <c r="DC55" t="s">
@@ -10387,99 +10521,99 @@
       <c r="AK56" s="10"/>
       <c r="AL56" s="10"/>
       <c r="AM56" s="10">
-        <f t="shared" ref="AM56:BF56" si="215">+AM42/AM41</f>
+        <f t="shared" ref="AM56:BF56" si="218">+AM42/AM41</f>
         <v>0.11105169340463458</v>
       </c>
       <c r="AN56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.12985685071574643</v>
       </c>
       <c r="AO56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.13108930987821379</v>
       </c>
       <c r="AP56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.13662024840045164</v>
       </c>
       <c r="AQ56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.33972098727579336</v>
       </c>
       <c r="AR56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.32435597189695553</v>
       </c>
       <c r="AS56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.16891799699822621</v>
       </c>
       <c r="AT56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.19849492856363835</v>
       </c>
       <c r="AU56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.16362395495649207</v>
       </c>
       <c r="AV56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.15543956940140272</v>
       </c>
       <c r="AW56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>3.5288331488995447E-2</v>
       </c>
       <c r="AX56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.14063577173496744</v>
       </c>
       <c r="AY56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.17438928975049986</v>
       </c>
       <c r="AZ56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.16934388236234316</v>
       </c>
       <c r="BA56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.12976810222432561</v>
       </c>
       <c r="BB56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.19028499448905684</v>
       </c>
       <c r="BC56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.1619892231701841</v>
       </c>
       <c r="BD56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.18311751771316884</v>
       </c>
       <c r="BE56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.21180057388809181</v>
       </c>
       <c r="BF56" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>0.24345422019840623</v>
       </c>
       <c r="BG56" s="10">
-        <f t="shared" ref="BG56:BJ56" si="216">+BG42/BG41</f>
+        <f t="shared" ref="BG56:BJ56" si="219">+BG42/BG41</f>
         <v>0.19</v>
       </c>
       <c r="BH56" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="219"/>
         <v>0.13482038878437697</v>
       </c>
       <c r="BI56" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="219"/>
         <v>0.1738231098430813</v>
       </c>
       <c r="BJ56" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="219"/>
         <v>0.17357299798690146</v>
       </c>
       <c r="BK56" s="10">
@@ -10487,35 +10621,35 @@
         <v>0.12789959811041388</v>
       </c>
       <c r="BL56" s="10">
-        <f t="shared" ref="BL56:BO56" si="217">+BL42/BL41</f>
+        <f t="shared" ref="BL56:BO56" si="220">+BL42/BL41</f>
         <v>0.10863233152389778</v>
       </c>
       <c r="BM56" s="10">
-        <f t="shared" si="217"/>
+        <f t="shared" si="220"/>
         <v>0.11973964762652901</v>
       </c>
       <c r="BN56" s="10">
-        <f t="shared" si="217"/>
+        <f t="shared" si="220"/>
         <v>0.11527193988027003</v>
       </c>
       <c r="BO56" s="10">
-        <f t="shared" si="217"/>
+        <f t="shared" si="220"/>
         <v>9.4549015341094556E-2</v>
       </c>
       <c r="BP56" s="10">
-        <f t="shared" ref="BP56:BR56" si="218">+BP42/BP41</f>
+        <f t="shared" ref="BP56:BR56" si="221">+BP42/BP41</f>
         <v>0.10699327943897925</v>
       </c>
       <c r="BQ56" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="221"/>
         <v>0</v>
       </c>
       <c r="BR56" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="221"/>
         <v>0.10199574031710973</v>
       </c>
       <c r="BS56" s="10">
-        <f t="shared" ref="BS56" si="219">+BS42/BS41</f>
+        <f t="shared" ref="BS56" si="222">+BS42/BS41</f>
         <v>0</v>
       </c>
       <c r="BT56" s="10"/>
@@ -10523,55 +10657,55 @@
       <c r="BV56" s="10"/>
       <c r="BW56" s="10"/>
       <c r="CM56" s="19">
-        <f t="shared" ref="CM56:CY56" si="220">+CM42/CM41</f>
+        <f t="shared" ref="CM56:CY56" si="223">+CM42/CM41</f>
         <v>0.12814952091794488</v>
       </c>
       <c r="CN56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.21222997450690997</v>
       </c>
       <c r="CO56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.12157926461723931</v>
       </c>
       <c r="CP56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.16737162676592504</v>
       </c>
       <c r="CQ56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="CR56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="CS56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="CT56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="CU56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="CV56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="CW56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.17999999999999997</v>
       </c>
       <c r="CX56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="CY56" s="19">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>0.18</v>
       </c>
       <c r="DC56" s="3" t="s">
@@ -10595,79 +10729,79 @@
         <v>195</v>
       </c>
       <c r="BA58" s="6">
-        <f t="shared" ref="BA58:BC58" si="221">+BA59-BA73</f>
+        <f t="shared" ref="BA58:BC58" si="224">+BA59-BA73</f>
         <v>64833</v>
       </c>
       <c r="BB58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="224"/>
         <v>54773</v>
       </c>
       <c r="BC58" s="6">
-        <f t="shared" si="221"/>
+        <f t="shared" si="224"/>
         <v>50665</v>
       </c>
       <c r="BD58" s="6">
-        <f t="shared" ref="BD58:BG58" si="222">+BD59-BD73</f>
+        <f t="shared" ref="BD58:BG58" si="225">+BD59-BD73</f>
         <v>47025</v>
       </c>
       <c r="BE58" s="6">
-        <f t="shared" si="222"/>
+        <f t="shared" si="225"/>
         <v>38382</v>
       </c>
       <c r="BF58" s="6">
-        <f t="shared" si="222"/>
+        <f t="shared" si="225"/>
         <v>37016</v>
       </c>
       <c r="BG58" s="6">
-        <f t="shared" si="222"/>
+        <f t="shared" si="225"/>
         <v>33681</v>
       </c>
       <c r="BH58" s="6">
-        <f t="shared" ref="BH58:BS58" si="223">+BH59-BH73</f>
+        <f t="shared" ref="BH58:BS58" si="226">+BH59-BH73</f>
         <v>41272</v>
       </c>
       <c r="BI58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>48882</v>
       </c>
       <c r="BJ58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>53159</v>
       </c>
       <c r="BK58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>45951</v>
       </c>
       <c r="BL58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>45898</v>
       </c>
       <c r="BM58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>48148</v>
       </c>
       <c r="BN58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>55059</v>
       </c>
       <c r="BO58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>47569</v>
       </c>
       <c r="BP58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>40227</v>
       </c>
       <c r="BQ58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>40688</v>
       </c>
       <c r="BR58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="BS58" s="6">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>50842</v>
       </c>
       <c r="BT58" s="6"/>
@@ -10830,35 +10964,35 @@
         <v>46939</v>
       </c>
       <c r="CR59" s="3">
-        <f t="shared" ref="CR59:CY59" si="224">+CQ59+CR43</f>
+        <f t="shared" ref="CR59:CY59" si="227">+CQ59+CR43</f>
         <v>101359.15280000001</v>
       </c>
       <c r="CS59" s="3">
-        <f t="shared" si="224"/>
+        <f t="shared" si="227"/>
         <v>177969.03700592002</v>
       </c>
       <c r="CT59" s="3">
-        <f t="shared" si="224"/>
+        <f t="shared" si="227"/>
         <v>281529.20290281717</v>
       </c>
       <c r="CU59" s="3">
-        <f t="shared" si="224"/>
+        <f t="shared" si="227"/>
         <v>401462.29475142341</v>
       </c>
       <c r="CV59" s="3">
-        <f t="shared" si="224"/>
+        <f t="shared" si="227"/>
         <v>536302.41270824685</v>
       </c>
       <c r="CW59" s="3">
-        <f t="shared" si="224"/>
+        <f t="shared" si="227"/>
         <v>687114.35795679211</v>
       </c>
       <c r="CX59" s="3">
-        <f t="shared" si="224"/>
+        <f t="shared" si="227"/>
         <v>849929.66682996857</v>
       </c>
       <c r="CY59" s="3">
-        <f t="shared" si="224"/>
+        <f t="shared" si="227"/>
         <v>1025276.6502334931</v>
       </c>
       <c r="DC59" s="3" t="s">
@@ -10988,7 +11122,7 @@
       </c>
       <c r="DD60" s="19">
         <f>DD59/Main!M2-1</f>
-        <v>0.1805205006856041</v>
+        <v>0.21465119543331723</v>
       </c>
     </row>
     <row r="61" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11631,23 +11765,23 @@
       <c r="AV66" s="6"/>
       <c r="AW66" s="6"/>
       <c r="AX66" s="6">
-        <f t="shared" ref="AX66:AY66" si="225">SUM(AX59:AX65)</f>
+        <f t="shared" ref="AX66:AY66" si="228">SUM(AX59:AX65)</f>
         <v>159316</v>
       </c>
       <c r="AY66" s="6">
-        <f t="shared" si="225"/>
+        <f t="shared" si="228"/>
         <v>163523</v>
       </c>
       <c r="AZ66" s="6">
-        <f t="shared" ref="AZ66:BA66" si="226">SUM(AZ59:AZ65)</f>
+        <f t="shared" ref="AZ66:BA66" si="229">SUM(AZ59:AZ65)</f>
         <v>170609</v>
       </c>
       <c r="BA66" s="6">
-        <f t="shared" si="226"/>
+        <f t="shared" si="229"/>
         <v>169585</v>
       </c>
       <c r="BB66" s="6">
-        <f t="shared" ref="BB66" si="227">SUM(BB59:BB65)</f>
+        <f t="shared" ref="BB66" si="230">SUM(BB59:BB65)</f>
         <v>165987</v>
       </c>
       <c r="BC66" s="6">
@@ -11663,59 +11797,59 @@
         <v>178894</v>
       </c>
       <c r="BF66" s="6">
-        <f t="shared" ref="BF66:BS66" si="228">SUM(BF59:BF65)</f>
+        <f t="shared" ref="BF66:BS66" si="231">SUM(BF59:BF65)</f>
         <v>185727</v>
       </c>
       <c r="BG66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>184491</v>
       </c>
       <c r="BH66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>206688</v>
       </c>
       <c r="BI66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>216274</v>
       </c>
       <c r="BJ66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>229623</v>
       </c>
       <c r="BK66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>222844</v>
       </c>
       <c r="BL66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>230238</v>
       </c>
       <c r="BM66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>256408</v>
       </c>
       <c r="BN66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>276054</v>
       </c>
       <c r="BO66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>280213</v>
       </c>
       <c r="BP66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>294744</v>
       </c>
       <c r="BQ66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>303844</v>
       </c>
       <c r="BR66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>0</v>
       </c>
       <c r="BS66" s="6">
-        <f t="shared" si="228"/>
+        <f t="shared" si="231"/>
         <v>395250</v>
       </c>
     </row>
@@ -12418,35 +12552,35 @@
         <v>61</v>
       </c>
       <c r="AX78" s="6">
-        <f t="shared" ref="AX78:AY78" si="229">SUM(AX68:AX77)</f>
+        <f t="shared" ref="AX78:AY78" si="232">SUM(AX68:AX77)</f>
         <v>159316</v>
       </c>
       <c r="AY78" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="232"/>
         <v>163523</v>
       </c>
       <c r="AZ78" s="6">
-        <f t="shared" ref="AZ78:BA78" si="230">SUM(AZ68:AZ77)</f>
+        <f t="shared" ref="AZ78:BA78" si="233">SUM(AZ68:AZ77)</f>
         <v>170609</v>
       </c>
       <c r="BA78" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="233"/>
         <v>169585</v>
       </c>
       <c r="BB78" s="6">
-        <f t="shared" ref="BB78:BE78" si="231">SUM(BB68:BB77)</f>
+        <f t="shared" ref="BB78:BE78" si="234">SUM(BB68:BB77)</f>
         <v>165987</v>
       </c>
       <c r="BC78" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="234"/>
         <v>164218</v>
       </c>
       <c r="BD78" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="234"/>
         <v>169779</v>
       </c>
       <c r="BE78" s="6">
-        <f t="shared" si="231"/>
+        <f t="shared" si="234"/>
         <v>178894</v>
       </c>
       <c r="BF78" s="6">
@@ -12470,39 +12604,39 @@
         <v>229623</v>
       </c>
       <c r="BK78" s="6">
-        <f t="shared" ref="BK78:BS78" si="232">SUM(BK68:BK77)</f>
+        <f t="shared" ref="BK78:BS78" si="235">SUM(BK68:BK77)</f>
         <v>222844</v>
       </c>
       <c r="BL78" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="235"/>
         <v>230238</v>
       </c>
       <c r="BM78" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="235"/>
         <v>256408</v>
       </c>
       <c r="BN78" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="235"/>
         <v>276054</v>
       </c>
       <c r="BO78" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="235"/>
         <v>280213</v>
       </c>
       <c r="BP78" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="235"/>
         <v>294744</v>
       </c>
       <c r="BQ78" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="235"/>
         <v>303844</v>
       </c>
       <c r="BR78" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="235"/>
         <v>0</v>
       </c>
       <c r="BS78" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="235"/>
         <v>395250</v>
       </c>
     </row>
@@ -12514,31 +12648,31 @@
         <v>66</v>
       </c>
       <c r="AY80" s="6">
-        <f t="shared" ref="AY80:BJ80" si="233">AY43</f>
+        <f t="shared" ref="AY80:BJ80" si="236">AY43</f>
         <v>9497</v>
       </c>
       <c r="AZ80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>10394</v>
       </c>
       <c r="BA80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>9194</v>
       </c>
       <c r="BB80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>10285</v>
       </c>
       <c r="BC80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>7465</v>
       </c>
       <c r="BD80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>6687</v>
       </c>
       <c r="BE80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>4395</v>
       </c>
       <c r="BF80" s="6">
@@ -12546,47 +12680,47 @@
         <v>4652</v>
       </c>
       <c r="BG80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>8374.1444999999985</v>
       </c>
       <c r="BH80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>9658</v>
       </c>
       <c r="BI80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>11583</v>
       </c>
       <c r="BJ80" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="236"/>
         <v>13288.690000000002</v>
       </c>
       <c r="BK80" s="6">
-        <f t="shared" ref="BK80:BQ80" si="234">BK43</f>
+        <f t="shared" ref="BK80:BQ80" si="237">BK43</f>
         <v>12369</v>
       </c>
       <c r="BL80" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="237"/>
         <v>13465</v>
       </c>
       <c r="BM80" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="237"/>
         <v>15688</v>
       </c>
       <c r="BN80" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="237"/>
         <v>20838</v>
       </c>
       <c r="BO80" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="237"/>
         <v>16644</v>
       </c>
       <c r="BP80" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="237"/>
         <v>18337</v>
       </c>
       <c r="BQ80" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="237"/>
         <v>21663</v>
       </c>
     </row>
@@ -13044,79 +13178,79 @@
         <v>68</v>
       </c>
       <c r="AY87" s="6">
-        <f t="shared" ref="AY87:BH87" si="235">SUM(AY81:AY86)</f>
+        <f t="shared" ref="AY87:BH87" si="238">SUM(AY81:AY86)</f>
         <v>12242</v>
       </c>
       <c r="AZ87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>13247</v>
       </c>
       <c r="BA87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>14090</v>
       </c>
       <c r="BB87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>18104</v>
       </c>
       <c r="BC87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>14076</v>
       </c>
       <c r="BD87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>12197</v>
       </c>
       <c r="BE87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>9691</v>
       </c>
       <c r="BF87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>14511</v>
       </c>
       <c r="BG87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>13998</v>
       </c>
       <c r="BH87" s="6">
-        <f t="shared" si="235"/>
+        <f t="shared" si="238"/>
         <v>17309</v>
       </c>
       <c r="BI87" s="6">
-        <f t="shared" ref="BI87:BQ87" si="236">SUM(BI81:BI86)</f>
+        <f t="shared" ref="BI87:BQ87" si="239">SUM(BI81:BI86)</f>
         <v>20402</v>
       </c>
       <c r="BJ87" s="6">
-        <f t="shared" si="236"/>
+        <f t="shared" si="239"/>
         <v>19404</v>
       </c>
       <c r="BK87" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="239"/>
         <v>19246</v>
       </c>
       <c r="BL87" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="239"/>
         <v>19370</v>
       </c>
       <c r="BM87" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="239"/>
         <v>24724</v>
       </c>
       <c r="BN87" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="239"/>
         <v>27988</v>
       </c>
       <c r="BO87" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="239"/>
         <v>24026</v>
       </c>
       <c r="BP87" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="239"/>
         <v>25561</v>
       </c>
       <c r="BQ87" s="3">
-        <f t="shared" si="236"/>
+        <f t="shared" si="239"/>
         <v>29999</v>
       </c>
       <c r="CE87" s="3">
@@ -13573,79 +13707,79 @@
       <c r="AW92" s="6"/>
       <c r="AX92" s="6"/>
       <c r="AY92" s="6">
-        <f t="shared" ref="AY92:BJ92" si="237">SUM(AY89:AY91)</f>
+        <f t="shared" ref="AY92:BJ92" si="240">SUM(AY89:AY91)</f>
         <v>-4874</v>
       </c>
       <c r="AZ92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-8195</v>
       </c>
       <c r="BA92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-330</v>
       </c>
       <c r="BB92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>5829</v>
       </c>
       <c r="BC92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-4779</v>
       </c>
       <c r="BD92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-6959</v>
       </c>
       <c r="BE92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-9701</v>
       </c>
       <c r="BF92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-7531</v>
       </c>
       <c r="BG92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-6743</v>
       </c>
       <c r="BH92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-5203</v>
       </c>
       <c r="BI92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-6077</v>
       </c>
       <c r="BJ92" s="6">
-        <f t="shared" si="237"/>
+        <f t="shared" si="240"/>
         <v>-6472</v>
       </c>
       <c r="BK92" s="3">
-        <f t="shared" ref="BK92:BQ92" si="238">SUM(BK89:BK91)</f>
+        <f t="shared" ref="BK92:BQ92" si="241">SUM(BK89:BK91)</f>
         <v>-8734</v>
       </c>
       <c r="BL92" s="3">
-        <f t="shared" si="238"/>
+        <f t="shared" si="241"/>
         <v>-8298</v>
       </c>
       <c r="BM92" s="3">
-        <f t="shared" si="238"/>
+        <f t="shared" si="241"/>
         <v>-8620</v>
       </c>
       <c r="BN92" s="3">
-        <f t="shared" si="238"/>
+        <f t="shared" si="241"/>
         <v>-21498</v>
       </c>
       <c r="BO92" s="3">
-        <f t="shared" si="238"/>
+        <f t="shared" si="241"/>
         <v>-20010</v>
       </c>
       <c r="BP92" s="3">
-        <f t="shared" si="238"/>
+        <f t="shared" si="241"/>
         <v>-25958</v>
       </c>
       <c r="BQ92" s="3">
-        <f t="shared" si="238"/>
+        <f t="shared" si="241"/>
         <v>-21848</v>
       </c>
     </row>
@@ -14334,79 +14468,79 @@
       <c r="AW99" s="6"/>
       <c r="AX99" s="6"/>
       <c r="AY99" s="6">
-        <f t="shared" ref="AY99:BA99" si="239">SUM(AY94:AY98)</f>
+        <f t="shared" ref="AY99:BA99" si="242">SUM(AY94:AY98)</f>
         <v>-5185</v>
       </c>
       <c r="AZ99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="242"/>
         <v>-8549</v>
       </c>
       <c r="BA99" s="6">
-        <f t="shared" si="239"/>
+        <f t="shared" si="242"/>
         <v>-15252</v>
       </c>
       <c r="BB99" s="6">
-        <f t="shared" ref="BB99" si="240">SUM(BB94:BB98)</f>
+        <f t="shared" ref="BB99" si="243">SUM(BB94:BB98)</f>
         <v>-21742</v>
       </c>
       <c r="BC99" s="6">
-        <f t="shared" ref="BC99:BQ99" si="241">SUM(BC94:BC98)</f>
+        <f t="shared" ref="BC99:BQ99" si="244">SUM(BC94:BC98)</f>
         <v>-10660</v>
       </c>
       <c r="BD99" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-6563</v>
       </c>
       <c r="BE99" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>2147</v>
       </c>
       <c r="BF99" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-7060</v>
       </c>
       <c r="BG99" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-10516</v>
       </c>
       <c r="BH99" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>5292</v>
       </c>
       <c r="BI99" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-5875</v>
       </c>
       <c r="BJ99" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-8401</v>
       </c>
       <c r="BK99" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-19767</v>
       </c>
       <c r="BL99" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-11178</v>
       </c>
       <c r="BM99" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-4371</v>
       </c>
       <c r="BN99" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-5465</v>
       </c>
       <c r="BO99" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-19495</v>
       </c>
       <c r="BP99" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-15977</v>
       </c>
       <c r="BQ99" s="3">
-        <f t="shared" si="241"/>
+        <f t="shared" si="244"/>
         <v>-10047</v>
       </c>
     </row>
@@ -14488,31 +14622,31 @@
         <v>81</v>
       </c>
       <c r="AY101" s="6">
-        <f t="shared" ref="AY101:BJ101" si="242">+AY100+AY99+AY92+AY87</f>
+        <f t="shared" ref="AY101:BJ101" si="245">+AY100+AY99+AY92+AY87</f>
         <v>1937</v>
       </c>
       <c r="AZ101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>-3380</v>
       </c>
       <c r="BA101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>-1707</v>
       </c>
       <c r="BB101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>2061</v>
       </c>
       <c r="BC101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>-1512</v>
       </c>
       <c r="BD101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>-1875</v>
       </c>
       <c r="BE101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>1773</v>
       </c>
       <c r="BF101" s="6">
@@ -14520,47 +14654,47 @@
         <v>345</v>
       </c>
       <c r="BG101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>-3176</v>
       </c>
       <c r="BH101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>17384</v>
       </c>
       <c r="BI101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>8096</v>
       </c>
       <c r="BJ101" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="245"/>
         <v>4927</v>
       </c>
       <c r="BK101" s="3">
-        <f t="shared" ref="BK101:BQ101" si="243">+BK100+BK99+BK92+BK87</f>
+        <f t="shared" ref="BK101:BQ101" si="246">+BK100+BK99+BK92+BK87</f>
         <v>-9543</v>
       </c>
       <c r="BL101" s="3">
-        <f t="shared" si="243"/>
+        <f t="shared" si="246"/>
         <v>-258</v>
       </c>
       <c r="BM101" s="3">
-        <f t="shared" si="243"/>
+        <f t="shared" si="246"/>
         <v>12101</v>
       </c>
       <c r="BN101" s="3">
-        <f t="shared" si="243"/>
+        <f t="shared" si="246"/>
         <v>311</v>
       </c>
       <c r="BO101" s="3">
-        <f t="shared" si="243"/>
+        <f t="shared" si="246"/>
         <v>-15367</v>
       </c>
       <c r="BP101" s="3">
-        <f t="shared" si="243"/>
+        <f t="shared" si="246"/>
         <v>-16243</v>
       </c>
       <c r="BQ101" s="3">
-        <f t="shared" si="243"/>
+        <f t="shared" si="246"/>
         <v>-1887</v>
       </c>
     </row>
@@ -14677,55 +14811,55 @@
         <v>199</v>
       </c>
       <c r="BC104" s="6">
-        <f t="shared" ref="BC104:BO104" si="244">+BC103-BB103</f>
+        <f t="shared" ref="BC104:BO104" si="247">+BC103-BB103</f>
         <v>5835</v>
       </c>
       <c r="BD104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>5748</v>
       </c>
       <c r="BE104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>3761</v>
       </c>
       <c r="BF104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>-1314</v>
       </c>
       <c r="BG104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>-8886</v>
       </c>
       <c r="BH104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>-5645</v>
       </c>
       <c r="BI104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>-5284</v>
       </c>
       <c r="BJ104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>1132</v>
       </c>
       <c r="BK104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>2012</v>
       </c>
       <c r="BL104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>1470</v>
       </c>
       <c r="BM104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>1605</v>
       </c>
       <c r="BN104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>1663</v>
       </c>
       <c r="BO104" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="247"/>
         <v>2767</v>
       </c>
     </row>
@@ -14742,51 +14876,51 @@
         <v>7970</v>
       </c>
       <c r="AZ106" s="6">
-        <f t="shared" ref="AZ106:BC106" si="245">+AZ87+AZ89</f>
+        <f t="shared" ref="AZ106:BC106" si="248">+AZ87+AZ89</f>
         <v>8635</v>
       </c>
       <c r="BA106" s="6">
-        <f t="shared" si="245"/>
+        <f t="shared" si="248"/>
         <v>9776</v>
       </c>
       <c r="BB106" s="6">
-        <f t="shared" si="245"/>
+        <f t="shared" si="248"/>
         <v>12734</v>
       </c>
       <c r="BC106" s="6">
-        <f t="shared" si="245"/>
+        <f t="shared" si="248"/>
         <v>8761</v>
       </c>
       <c r="BD106" s="6">
-        <f t="shared" ref="BD106:BJ106" si="246">+BD87+BD89</f>
+        <f t="shared" ref="BD106:BJ106" si="249">+BD87+BD89</f>
         <v>4669</v>
       </c>
       <c r="BE106" s="6">
-        <f t="shared" si="246"/>
+        <f t="shared" si="249"/>
         <v>336</v>
       </c>
       <c r="BF106" s="6">
-        <f t="shared" si="246"/>
+        <f t="shared" si="249"/>
         <v>5523</v>
       </c>
       <c r="BG106" s="6">
-        <f t="shared" si="246"/>
+        <f t="shared" si="249"/>
         <v>7175</v>
       </c>
       <c r="BH106" s="6">
-        <f t="shared" si="246"/>
+        <f t="shared" si="249"/>
         <v>11175</v>
       </c>
       <c r="BI106" s="6">
-        <f t="shared" si="246"/>
+        <f t="shared" si="249"/>
         <v>13906</v>
       </c>
       <c r="BJ106" s="6">
-        <f t="shared" si="246"/>
+        <f t="shared" si="249"/>
         <v>11812</v>
       </c>
       <c r="BK106" s="3">
-        <f t="shared" ref="BK106" si="247">+BK87+BK89</f>
+        <f t="shared" ref="BK106" si="250">+BK87+BK89</f>
         <v>12846</v>
       </c>
       <c r="BL106" s="3">
@@ -14806,11 +14940,11 @@
         <v>11085</v>
       </c>
       <c r="BP106" s="3">
-        <f t="shared" ref="BP106:BQ106" si="248">+BP87+BP89</f>
+        <f t="shared" ref="BP106:BQ106" si="251">+BP87+BP89</f>
         <v>9023</v>
       </c>
       <c r="BQ106" s="3">
-        <f t="shared" si="248"/>
+        <f t="shared" si="251"/>
         <v>11170</v>
       </c>
     </row>
@@ -14819,11 +14953,11 @@
         <v>127</v>
       </c>
       <c r="BB107" s="6">
-        <f t="shared" ref="BB107:BC107" si="249">SUM(AY106:BB106)</f>
+        <f t="shared" ref="BB107:BC107" si="252">SUM(AY106:BB106)</f>
         <v>39115</v>
       </c>
       <c r="BC107" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="252"/>
         <v>39906</v>
       </c>
       <c r="BD107" s="6">
@@ -14839,31 +14973,31 @@
         <v>19289</v>
       </c>
       <c r="BG107" s="6">
-        <f t="shared" ref="BG107:BK107" si="250">SUM(BD106:BG106)</f>
+        <f t="shared" ref="BG107:BK107" si="253">SUM(BD106:BG106)</f>
         <v>17703</v>
       </c>
       <c r="BH107" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="253"/>
         <v>24209</v>
       </c>
       <c r="BI107" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="253"/>
         <v>37779</v>
       </c>
       <c r="BJ107" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="253"/>
         <v>44068</v>
       </c>
       <c r="BK107" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="253"/>
         <v>49739</v>
       </c>
       <c r="BL107" s="3">
-        <f t="shared" ref="BL107:BM107" si="251">SUM(BI106:BL106)</f>
+        <f t="shared" ref="BL107:BM107" si="254">SUM(BI106:BL106)</f>
         <v>49761</v>
       </c>
       <c r="BM107" s="3">
-        <f t="shared" si="251"/>
+        <f t="shared" si="254"/>
         <v>52321</v>
       </c>
       <c r="BN107" s="3">
@@ -14875,11 +15009,11 @@
         <v>52311</v>
       </c>
       <c r="BP107" s="3">
-        <f t="shared" ref="BP107:BQ107" si="252">SUM(BM106:BP106)</f>
+        <f t="shared" ref="BP107:BQ107" si="255">SUM(BM106:BP106)</f>
         <v>50137</v>
       </c>
       <c r="BQ107" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="255"/>
         <v>44841</v>
       </c>
     </row>
@@ -14905,11 +15039,11 @@
         <v>0.3108555104495565</v>
       </c>
       <c r="BP108" s="19">
-        <f t="shared" ref="BP108:BQ108" si="253">+BP107/BD107-1</f>
+        <f t="shared" ref="BP108:BQ108" si="256">+BP107/BD107-1</f>
         <v>0.39501947690595429</v>
       </c>
       <c r="BQ108" s="19">
-        <f t="shared" si="253"/>
+        <f t="shared" si="256"/>
         <v>0.69211320754716987</v>
       </c>
     </row>
@@ -14938,59 +15072,59 @@
         <v>94400</v>
       </c>
       <c r="AZ110" s="3">
-        <f t="shared" ref="AZ110:BM110" si="254">SUM(AW32:AZ32)</f>
+        <f t="shared" ref="AZ110:BM110" si="257">SUM(AW32:AZ32)</f>
         <v>104790</v>
       </c>
       <c r="BA110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>112330</v>
       </c>
       <c r="BB110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>117929</v>
       </c>
       <c r="BC110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>119666</v>
       </c>
       <c r="BD110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>119411</v>
       </c>
       <c r="BE110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>118115</v>
       </c>
       <c r="BF110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>116609</v>
       </c>
       <c r="BG110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>117346</v>
       </c>
       <c r="BH110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>120523</v>
       </c>
       <c r="BI110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>126955</v>
       </c>
       <c r="BJ110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>134901</v>
       </c>
       <c r="BK110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>142711</v>
       </c>
       <c r="BL110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>149783</v>
       </c>
       <c r="BM110" s="3">
-        <f t="shared" si="254"/>
+        <f t="shared" si="257"/>
         <v>156226</v>
       </c>
       <c r="BN110" s="3">
